--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -442,12 +442,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -824,17 +824,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kv_cache_eviction</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ollama</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -848,41 +848,47 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.309</v>
+        <v>0.586</v>
       </c>
       <c r="G8" t="n">
-        <v>3.63</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>86.642</v>
+        <v>54.59</v>
       </c>
       <c r="I8" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J8" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K8" t="n">
-        <v>60</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kv_cache_eviction</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ollama</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -896,41 +902,47 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.194</v>
+        <v>0.572</v>
       </c>
       <c r="G9" t="n">
-        <v>3.513</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>87.744</v>
+        <v>55.9</v>
       </c>
       <c r="I9" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J9" t="n">
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K9" t="n">
-        <v>60</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kv_cache_eviction</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ollama</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -944,41 +956,47 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.658</v>
+        <v>1.03</v>
       </c>
       <c r="G10" t="n">
-        <v>2.252</v>
+        <v>1.358</v>
       </c>
       <c r="H10" t="n">
-        <v>89.47499999999999</v>
+        <v>31.07</v>
       </c>
       <c r="I10" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J10" t="n">
-        <v>873.5</v>
+        <v>854</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kv_cache_eviction</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ollama</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -992,41 +1010,47 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.653</v>
+        <v>1.237</v>
       </c>
       <c r="G11" t="n">
-        <v>2.424</v>
+        <v>1.264</v>
       </c>
       <c r="H11" t="n">
-        <v>89.398</v>
+        <v>25.88</v>
       </c>
       <c r="I11" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J11" t="n">
-        <v>784.5</v>
+        <v>789</v>
       </c>
       <c r="K11" t="n">
-        <v>60</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kv_cache_eviction</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ollama</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1040,41 +1064,47 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.641</v>
+        <v>1.332</v>
       </c>
       <c r="G12" t="n">
-        <v>1.755</v>
+        <v>1.577</v>
       </c>
       <c r="H12" t="n">
-        <v>89.95699999999999</v>
+        <v>24.03</v>
       </c>
       <c r="I12" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="J12" t="n">
-        <v>89.5</v>
+        <v>72</v>
       </c>
       <c r="K12" t="n">
-        <v>60</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kv_cache_eviction</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ollama</t>
+          <t>huggingface</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1088,26 +1118,644 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="H13" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="I13" t="n">
+        <v>32</v>
+      </c>
+      <c r="J13" t="n">
+        <v>163</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="H14" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="I14" t="n">
+        <v>32</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="I15" t="n">
+        <v>32</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="H16" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="I16" t="n">
+        <v>32</v>
+      </c>
+      <c r="J16" t="n">
+        <v>854</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="H17" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="I17" t="n">
+        <v>32</v>
+      </c>
+      <c r="J17" t="n">
+        <v>789</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.396</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.398</v>
+      </c>
+      <c r="H18" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="I18" t="n">
+        <v>32</v>
+      </c>
+      <c r="J18" t="n">
+        <v>72</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.876</v>
+      </c>
+      <c r="H19" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="I19" t="n">
+        <v>32</v>
+      </c>
+      <c r="J19" t="n">
+        <v>163</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>kv_cache_eviction</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3.309</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H20" t="n">
+        <v>86.642</v>
+      </c>
+      <c r="I20" t="n">
+        <v>128</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K20" t="n">
+        <v>60</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>kv_cache_eviction</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.513</v>
+      </c>
+      <c r="H21" t="n">
+        <v>87.744</v>
+      </c>
+      <c r="I21" t="n">
+        <v>128</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K21" t="n">
+        <v>60</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>kv_cache_eviction</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.252</v>
+      </c>
+      <c r="H22" t="n">
+        <v>89.47499999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>128</v>
+      </c>
+      <c r="J22" t="n">
+        <v>873.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>60</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>kv_cache_eviction</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.653</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.424</v>
+      </c>
+      <c r="H23" t="n">
+        <v>89.398</v>
+      </c>
+      <c r="I23" t="n">
+        <v>128</v>
+      </c>
+      <c r="J23" t="n">
+        <v>784.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>60</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>kv_cache_eviction</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="H24" t="n">
+        <v>89.95699999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>128</v>
+      </c>
+      <c r="J24" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>60</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>kv_cache_eviction</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ollama</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>1.717</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G25" t="n">
         <v>3.262</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H25" t="n">
         <v>88.32899999999999</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I25" t="n">
         <v>128</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J25" t="n">
         <v>194.5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K25" t="n">
         <v>60</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1120,7 +1768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1170,16 +1818,48 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.071</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.152</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>3.272</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>1.654</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>1.662</v>
       </c>
     </row>
@@ -1194,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1244,16 +1924,48 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
+          <t>hf_baseline</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>86.90000000000001</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C5" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>89.8</v>
       </c>
     </row>
@@ -1268,11 +1980,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1312,12 +2024,44 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>kvcache_limited_512</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.947</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>kvcache_limited_512</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1330,20 +2074,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K541"/>
+  <dimension ref="A1:K577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24622,6 +25366,1770 @@
       <c r="I541" t="inlineStr"/>
       <c r="J541" t="inlineStr"/>
       <c r="K541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>cnn_short_1</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>1</v>
+      </c>
+      <c r="I542" t="n">
+        <v>1</v>
+      </c>
+      <c r="J542" t="n">
+        <v>1</v>
+      </c>
+      <c r="K542" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>cnn_short_1</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>1</v>
+      </c>
+      <c r="I543" t="n">
+        <v>1</v>
+      </c>
+      <c r="J543" t="n">
+        <v>1</v>
+      </c>
+      <c r="K543" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>cnn_short_2</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>1</v>
+      </c>
+      <c r="I544" t="n">
+        <v>1</v>
+      </c>
+      <c r="J544" t="n">
+        <v>1</v>
+      </c>
+      <c r="K544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>cnn_short_2</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>1</v>
+      </c>
+      <c r="I545" t="n">
+        <v>1</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1</v>
+      </c>
+      <c r="K545" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>cnn_short_3</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>1</v>
+      </c>
+      <c r="I546" t="n">
+        <v>1</v>
+      </c>
+      <c r="J546" t="n">
+        <v>1</v>
+      </c>
+      <c r="K546" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>cnn_short_3</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>1</v>
+      </c>
+      <c r="I547" t="n">
+        <v>1</v>
+      </c>
+      <c r="J547" t="n">
+        <v>1</v>
+      </c>
+      <c r="K547" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>cnn_medium_1</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>1</v>
+      </c>
+      <c r="I548" t="n">
+        <v>1</v>
+      </c>
+      <c r="J548" t="n">
+        <v>1</v>
+      </c>
+      <c r="K548" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>cnn_medium_1</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>1</v>
+      </c>
+      <c r="I549" t="n">
+        <v>1</v>
+      </c>
+      <c r="J549" t="n">
+        <v>1</v>
+      </c>
+      <c r="K549" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>cnn_medium_2</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>1</v>
+      </c>
+      <c r="I550" t="n">
+        <v>1</v>
+      </c>
+      <c r="J550" t="n">
+        <v>1</v>
+      </c>
+      <c r="K550" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>cnn_medium_2</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>1</v>
+      </c>
+      <c r="J551" t="n">
+        <v>1</v>
+      </c>
+      <c r="K551" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>cnn_medium_3</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>1</v>
+      </c>
+      <c r="I552" t="n">
+        <v>1</v>
+      </c>
+      <c r="J552" t="n">
+        <v>1</v>
+      </c>
+      <c r="K552" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>cnn_medium_3</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>1</v>
+      </c>
+      <c r="I553" t="n">
+        <v>1</v>
+      </c>
+      <c r="J553" t="n">
+        <v>1</v>
+      </c>
+      <c r="K553" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>govreport_long_1</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>1</v>
+      </c>
+      <c r="I554" t="n">
+        <v>1</v>
+      </c>
+      <c r="J554" t="n">
+        <v>1</v>
+      </c>
+      <c r="K554" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>govreport_long_1</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>1</v>
+      </c>
+      <c r="I555" t="n">
+        <v>1</v>
+      </c>
+      <c r="J555" t="n">
+        <v>1</v>
+      </c>
+      <c r="K555" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>govreport_long_2</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>1</v>
+      </c>
+      <c r="I556" t="n">
+        <v>1</v>
+      </c>
+      <c r="J556" t="n">
+        <v>1</v>
+      </c>
+      <c r="K556" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>govreport_long_2</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>1</v>
+      </c>
+      <c r="I557" t="n">
+        <v>0</v>
+      </c>
+      <c r="J557" t="n">
+        <v>0.0947867298578199</v>
+      </c>
+      <c r="K557" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>govreport_long_3</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>1</v>
+      </c>
+      <c r="I558" t="n">
+        <v>1</v>
+      </c>
+      <c r="J558" t="n">
+        <v>1</v>
+      </c>
+      <c r="K558" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>govreport_long_3</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>1</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0.1409691629955947</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>gsm8k_short_1</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>1</v>
+      </c>
+      <c r="I560" t="n">
+        <v>1</v>
+      </c>
+      <c r="J560" t="n">
+        <v>1</v>
+      </c>
+      <c r="K560" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>gsm8k_short_1</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>1</v>
+      </c>
+      <c r="I561" t="n">
+        <v>1</v>
+      </c>
+      <c r="J561" t="n">
+        <v>1</v>
+      </c>
+      <c r="K561" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>gsm8k_short_2</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>1</v>
+      </c>
+      <c r="I562" t="n">
+        <v>1</v>
+      </c>
+      <c r="J562" t="n">
+        <v>1</v>
+      </c>
+      <c r="K562" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>gsm8k_short_2</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>1</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" t="n">
+        <v>0.7068273092369478</v>
+      </c>
+      <c r="K563" t="n">
+        <v>0.6818181818181819</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>gsm8k_short_3</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>1</v>
+      </c>
+      <c r="I564" t="n">
+        <v>1</v>
+      </c>
+      <c r="J564" t="n">
+        <v>1</v>
+      </c>
+      <c r="K564" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>gsm8k_short_3</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>1</v>
+      </c>
+      <c r="I565" t="n">
+        <v>1</v>
+      </c>
+      <c r="J565" t="n">
+        <v>1</v>
+      </c>
+      <c r="K565" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_1</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>1</v>
+      </c>
+      <c r="I566" t="n">
+        <v>1</v>
+      </c>
+      <c r="J566" t="n">
+        <v>1</v>
+      </c>
+      <c r="K566" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_1</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>1</v>
+      </c>
+      <c r="I567" t="n">
+        <v>1</v>
+      </c>
+      <c r="J567" t="n">
+        <v>1</v>
+      </c>
+      <c r="K567" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_2</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>1</v>
+      </c>
+      <c r="I568" t="n">
+        <v>1</v>
+      </c>
+      <c r="J568" t="n">
+        <v>1</v>
+      </c>
+      <c r="K568" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_2</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" t="n">
+        <v>1</v>
+      </c>
+      <c r="J569" t="n">
+        <v>1</v>
+      </c>
+      <c r="K569" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_3</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" t="n">
+        <v>1</v>
+      </c>
+      <c r="J570" t="n">
+        <v>1</v>
+      </c>
+      <c r="K570" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_3</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>1</v>
+      </c>
+      <c r="I571" t="n">
+        <v>1</v>
+      </c>
+      <c r="J571" t="n">
+        <v>1</v>
+      </c>
+      <c r="K571" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>gsm8k_long_1</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>1</v>
+      </c>
+      <c r="I572" t="n">
+        <v>1</v>
+      </c>
+      <c r="J572" t="n">
+        <v>1</v>
+      </c>
+      <c r="K572" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>gsm8k_long_1</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>1</v>
+      </c>
+      <c r="I573" t="n">
+        <v>1</v>
+      </c>
+      <c r="J573" t="n">
+        <v>1</v>
+      </c>
+      <c r="K573" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>gsm8k_long_2</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>1</v>
+      </c>
+      <c r="I574" t="n">
+        <v>1</v>
+      </c>
+      <c r="J574" t="n">
+        <v>1</v>
+      </c>
+      <c r="K574" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>gsm8k_long_2</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>1</v>
+      </c>
+      <c r="I575" t="n">
+        <v>0</v>
+      </c>
+      <c r="J575" t="n">
+        <v>0.05447470817120623</v>
+      </c>
+      <c r="K575" t="n">
+        <v>0.0689655172413793</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>gsm8k_long_3</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>1</v>
+      </c>
+      <c r="I576" t="n">
+        <v>1</v>
+      </c>
+      <c r="J576" t="n">
+        <v>1</v>
+      </c>
+      <c r="K576" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>gsm8k_long_3</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>1</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" t="n">
+        <v>0.05447470817120623</v>
+      </c>
+      <c r="K577" t="n">
+        <v>0.0689655172413793</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24634,13 +27142,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N541"/>
+  <dimension ref="A1:N577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -56045,6 +58553,2094 @@
         <v>25.453125</v>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>cnn_short_1</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>1</v>
+      </c>
+      <c r="I542" t="n">
+        <v>163</v>
+      </c>
+      <c r="J542" t="n">
+        <v>32</v>
+      </c>
+      <c r="K542" t="n">
+        <v>1.0996</v>
+      </c>
+      <c r="L542" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="M542" t="n">
+        <v>1055.5</v>
+      </c>
+      <c r="N542" t="n">
+        <v>1283.5</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>cnn_short_1</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>1</v>
+      </c>
+      <c r="I543" t="n">
+        <v>163</v>
+      </c>
+      <c r="J543" t="n">
+        <v>32</v>
+      </c>
+      <c r="K543" t="n">
+        <v>1.8959</v>
+      </c>
+      <c r="L543" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="M543" t="n">
+        <v>1283.5</v>
+      </c>
+      <c r="N543" t="n">
+        <v>1328.2</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>cnn_short_2</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>1</v>
+      </c>
+      <c r="I544" t="n">
+        <v>156</v>
+      </c>
+      <c r="J544" t="n">
+        <v>32</v>
+      </c>
+      <c r="K544" t="n">
+        <v>0.7282</v>
+      </c>
+      <c r="L544" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="M544" t="n">
+        <v>1328.2</v>
+      </c>
+      <c r="N544" t="n">
+        <v>1374.1</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>cnn_short_2</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>1</v>
+      </c>
+      <c r="I545" t="n">
+        <v>156</v>
+      </c>
+      <c r="J545" t="n">
+        <v>32</v>
+      </c>
+      <c r="K545" t="n">
+        <v>0.9068000000000001</v>
+      </c>
+      <c r="L545" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="M545" t="n">
+        <v>1374.1</v>
+      </c>
+      <c r="N545" t="n">
+        <v>1387.7</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>cnn_short_3</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>1</v>
+      </c>
+      <c r="I546" t="n">
+        <v>188</v>
+      </c>
+      <c r="J546" t="n">
+        <v>32</v>
+      </c>
+      <c r="K546" t="n">
+        <v>1.0432</v>
+      </c>
+      <c r="L546" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="M546" t="n">
+        <v>1387.8</v>
+      </c>
+      <c r="N546" t="n">
+        <v>1526.2</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>cnn_short_3</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>1</v>
+      </c>
+      <c r="I547" t="n">
+        <v>188</v>
+      </c>
+      <c r="J547" t="n">
+        <v>32</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0.7202</v>
+      </c>
+      <c r="L547" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="M547" t="n">
+        <v>1526.2</v>
+      </c>
+      <c r="N547" t="n">
+        <v>1556.9</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>cnn_medium_1</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>1</v>
+      </c>
+      <c r="I548" t="n">
+        <v>725</v>
+      </c>
+      <c r="J548" t="n">
+        <v>32</v>
+      </c>
+      <c r="K548" t="n">
+        <v>1.2366</v>
+      </c>
+      <c r="L548" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="M548" t="n">
+        <v>1557.1</v>
+      </c>
+      <c r="N548" t="n">
+        <v>1733.2</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>cnn_medium_1</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>1</v>
+      </c>
+      <c r="I549" t="n">
+        <v>725</v>
+      </c>
+      <c r="J549" t="n">
+        <v>32</v>
+      </c>
+      <c r="K549" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="L549" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="M549" t="n">
+        <v>1733.2</v>
+      </c>
+      <c r="N549" t="n">
+        <v>1767.3</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>cnn_medium_2</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>1</v>
+      </c>
+      <c r="I550" t="n">
+        <v>789</v>
+      </c>
+      <c r="J550" t="n">
+        <v>32</v>
+      </c>
+      <c r="K550" t="n">
+        <v>1.2645</v>
+      </c>
+      <c r="L550" t="n">
+        <v>25.31</v>
+      </c>
+      <c r="M550" t="n">
+        <v>1767.6</v>
+      </c>
+      <c r="N550" t="n">
+        <v>1942.5</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>cnn_medium_2</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>789</v>
+      </c>
+      <c r="J551" t="n">
+        <v>32</v>
+      </c>
+      <c r="K551" t="n">
+        <v>0.6775</v>
+      </c>
+      <c r="L551" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="M551" t="n">
+        <v>1942.5</v>
+      </c>
+      <c r="N551" t="n">
+        <v>1972.8</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>cnn_medium_3</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>1</v>
+      </c>
+      <c r="I552" t="n">
+        <v>803</v>
+      </c>
+      <c r="J552" t="n">
+        <v>32</v>
+      </c>
+      <c r="K552" t="n">
+        <v>1.0198</v>
+      </c>
+      <c r="L552" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="M552" t="n">
+        <v>1973.2</v>
+      </c>
+      <c r="N552" t="n">
+        <v>2055.4</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>cnn_medium_3</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>1</v>
+      </c>
+      <c r="I553" t="n">
+        <v>803</v>
+      </c>
+      <c r="J553" t="n">
+        <v>32</v>
+      </c>
+      <c r="K553" t="n">
+        <v>0.7629</v>
+      </c>
+      <c r="L553" t="n">
+        <v>41.94</v>
+      </c>
+      <c r="M553" t="n">
+        <v>2055.4</v>
+      </c>
+      <c r="N553" t="n">
+        <v>2085.8</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>govreport_long_1</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>1</v>
+      </c>
+      <c r="I554" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J554" t="n">
+        <v>32</v>
+      </c>
+      <c r="K554" t="n">
+        <v>1.4164</v>
+      </c>
+      <c r="L554" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="M554" t="n">
+        <v>2090.3</v>
+      </c>
+      <c r="N554" t="n">
+        <v>2263.8</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>govreport_long_1</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>1</v>
+      </c>
+      <c r="I555" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J555" t="n">
+        <v>32</v>
+      </c>
+      <c r="K555" t="n">
+        <v>0.8154</v>
+      </c>
+      <c r="L555" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="M555" t="n">
+        <v>2263.8</v>
+      </c>
+      <c r="N555" t="n">
+        <v>2294.1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>govreport_long_2</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>1</v>
+      </c>
+      <c r="I556" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J556" t="n">
+        <v>32</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L556" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="M556" t="n">
+        <v>2297.8</v>
+      </c>
+      <c r="N556" t="n">
+        <v>2298.9</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>govreport_long_2</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>1</v>
+      </c>
+      <c r="I557" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J557" t="n">
+        <v>32</v>
+      </c>
+      <c r="K557" t="n">
+        <v>0.6082</v>
+      </c>
+      <c r="L557" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="M557" t="n">
+        <v>2298.9</v>
+      </c>
+      <c r="N557" t="n">
+        <v>2301.1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>govreport_long_3</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>1</v>
+      </c>
+      <c r="I558" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J558" t="n">
+        <v>32</v>
+      </c>
+      <c r="K558" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="L558" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="M558" t="n">
+        <v>2301.9</v>
+      </c>
+      <c r="N558" t="n">
+        <v>2302.9</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>govreport_long_3</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>summarization</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>1</v>
+      </c>
+      <c r="I559" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J559" t="n">
+        <v>32</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0.6027</v>
+      </c>
+      <c r="L559" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="M559" t="n">
+        <v>2302.9</v>
+      </c>
+      <c r="N559" t="n">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>gsm8k_short_1</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>1</v>
+      </c>
+      <c r="I560" t="n">
+        <v>80</v>
+      </c>
+      <c r="J560" t="n">
+        <v>32</v>
+      </c>
+      <c r="K560" t="n">
+        <v>1.5815</v>
+      </c>
+      <c r="L560" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="M560" t="n">
+        <v>2304</v>
+      </c>
+      <c r="N560" t="n">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>gsm8k_short_1</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>1</v>
+      </c>
+      <c r="I561" t="n">
+        <v>80</v>
+      </c>
+      <c r="J561" t="n">
+        <v>32</v>
+      </c>
+      <c r="K561" t="n">
+        <v>1.3964</v>
+      </c>
+      <c r="L561" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="M561" t="n">
+        <v>2457</v>
+      </c>
+      <c r="N561" t="n">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>gsm8k_short_2</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>1</v>
+      </c>
+      <c r="I562" t="n">
+        <v>41</v>
+      </c>
+      <c r="J562" t="n">
+        <v>32</v>
+      </c>
+      <c r="K562" t="n">
+        <v>1.3317</v>
+      </c>
+      <c r="L562" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="M562" t="n">
+        <v>2490</v>
+      </c>
+      <c r="N562" t="n">
+        <v>2663.7</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>gsm8k_short_2</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>1</v>
+      </c>
+      <c r="I563" t="n">
+        <v>41</v>
+      </c>
+      <c r="J563" t="n">
+        <v>32</v>
+      </c>
+      <c r="K563" t="n">
+        <v>1.3985</v>
+      </c>
+      <c r="L563" t="n">
+        <v>22.88</v>
+      </c>
+      <c r="M563" t="n">
+        <v>2663.7</v>
+      </c>
+      <c r="N563" t="n">
+        <v>2699.4</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>gsm8k_short_3</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>1</v>
+      </c>
+      <c r="I564" t="n">
+        <v>72</v>
+      </c>
+      <c r="J564" t="n">
+        <v>32</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0.7921</v>
+      </c>
+      <c r="L564" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="M564" t="n">
+        <v>2699.5</v>
+      </c>
+      <c r="N564" t="n">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>gsm8k_short_3</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>1</v>
+      </c>
+      <c r="I565" t="n">
+        <v>72</v>
+      </c>
+      <c r="J565" t="n">
+        <v>32</v>
+      </c>
+      <c r="K565" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="L565" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="M565" t="n">
+        <v>2745</v>
+      </c>
+      <c r="N565" t="n">
+        <v>2755.5</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_1</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>1</v>
+      </c>
+      <c r="I566" t="n">
+        <v>854</v>
+      </c>
+      <c r="J566" t="n">
+        <v>32</v>
+      </c>
+      <c r="K566" t="n">
+        <v>1.3647</v>
+      </c>
+      <c r="L566" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="M566" t="n">
+        <v>2755.7</v>
+      </c>
+      <c r="N566" t="n">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_1</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>1</v>
+      </c>
+      <c r="I567" t="n">
+        <v>854</v>
+      </c>
+      <c r="J567" t="n">
+        <v>32</v>
+      </c>
+      <c r="K567" t="n">
+        <v>1.5417</v>
+      </c>
+      <c r="L567" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="M567" t="n">
+        <v>2930</v>
+      </c>
+      <c r="N567" t="n">
+        <v>2963.4</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_2</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>1</v>
+      </c>
+      <c r="I568" t="n">
+        <v>847</v>
+      </c>
+      <c r="J568" t="n">
+        <v>32</v>
+      </c>
+      <c r="K568" t="n">
+        <v>1.0299</v>
+      </c>
+      <c r="L568" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="M568" t="n">
+        <v>2963.8</v>
+      </c>
+      <c r="N568" t="n">
+        <v>3010.1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_2</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" t="n">
+        <v>847</v>
+      </c>
+      <c r="J569" t="n">
+        <v>32</v>
+      </c>
+      <c r="K569" t="n">
+        <v>0.8756</v>
+      </c>
+      <c r="L569" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="M569" t="n">
+        <v>3010.1</v>
+      </c>
+      <c r="N569" t="n">
+        <v>3020.6</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_3</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" t="n">
+        <v>864</v>
+      </c>
+      <c r="J570" t="n">
+        <v>32</v>
+      </c>
+      <c r="K570" t="n">
+        <v>0.8339</v>
+      </c>
+      <c r="L570" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="M570" t="n">
+        <v>3020.9</v>
+      </c>
+      <c r="N570" t="n">
+        <v>3081.9</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>gsm8k_medium_3</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>1</v>
+      </c>
+      <c r="I571" t="n">
+        <v>864</v>
+      </c>
+      <c r="J571" t="n">
+        <v>32</v>
+      </c>
+      <c r="K571" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="L571" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="M571" t="n">
+        <v>3081.9</v>
+      </c>
+      <c r="N571" t="n">
+        <v>3095.7</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>gsm8k_long_1</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>1</v>
+      </c>
+      <c r="I572" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J572" t="n">
+        <v>32</v>
+      </c>
+      <c r="K572" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="L572" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="M572" t="n">
+        <v>3098.9</v>
+      </c>
+      <c r="N572" t="n">
+        <v>3099.9</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>gsm8k_long_1</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>1</v>
+      </c>
+      <c r="I573" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J573" t="n">
+        <v>32</v>
+      </c>
+      <c r="K573" t="n">
+        <v>0.6074000000000001</v>
+      </c>
+      <c r="L573" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="M573" t="n">
+        <v>3099.9</v>
+      </c>
+      <c r="N573" t="n">
+        <v>3101.1</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>gsm8k_long_2</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>1</v>
+      </c>
+      <c r="I574" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J574" t="n">
+        <v>32</v>
+      </c>
+      <c r="K574" t="n">
+        <v>0.5861</v>
+      </c>
+      <c r="L574" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="M574" t="n">
+        <v>3101.2</v>
+      </c>
+      <c r="N574" t="n">
+        <v>3102.2</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>gsm8k_long_2</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>1</v>
+      </c>
+      <c r="I575" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J575" t="n">
+        <v>32</v>
+      </c>
+      <c r="K575" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="L575" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="M575" t="n">
+        <v>3102.2</v>
+      </c>
+      <c r="N575" t="n">
+        <v>3103.3</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>hf_baseline</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>gsm8k_long_3</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>1</v>
+      </c>
+      <c r="I576" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J576" t="n">
+        <v>32</v>
+      </c>
+      <c r="K576" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L576" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="M576" t="n">
+        <v>3103.6</v>
+      </c>
+      <c r="N576" t="n">
+        <v>3104.5</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>hf_sinkcache</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>sinkcache</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>huggingface</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Qwen/Qwen2.5-0.5B-Instruct</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>gsm8k_long_3</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>reasoning</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>1</v>
+      </c>
+      <c r="I577" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J577" t="n">
+        <v>32</v>
+      </c>
+      <c r="K577" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="L577" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="M577" t="n">
+        <v>3104.5</v>
+      </c>
+      <c r="N577" t="n">
+        <v>3105.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
